--- a/Project 2048/Reports/Project2048_SkillVfxInventory.xlsx
+++ b/Project 2048/Reports/Project2048_SkillVfxInventory.xlsx
@@ -146,12 +146,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>이펙트 프리팽 개수</t>
+          <t>이펙트 프리팹 개수</t>
         </is>
       </c>
     </row>
@@ -1026,17 +1026,17 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>화염 폭발 / 대표=화염 폭발; 투사체=성화 투사체 / 파티클=화염 폭발</t>
+          <t>화염 폭발 / 대표=화염 폭발; 투사체=파이어볼 VFX 그래프 / 파티클=화염 폭발</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>대표=화염 폭발; 투사체=성화 투사체</t>
+          <t>대표=화염 폭발; 투사체=파이어볼 VFX 그래프</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>primary=SkillVFX/Prefabs/SkillVfx_FlameBurst.prefab; projectile=SkillVFX/Prefabs/HolyFireball_Attack3.prefab</t>
+          <t>primary=SkillVFX/Prefabs/SkillVfx_FlameBurst.prefab; projectile=VFX Test/Prefab/vfx_Fireball_vfxgraph.prefab</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Assets/Data/Skills/BleedingCut.asset</t>
+          <t>Assets/Data/Skills/Fireball.asset</t>
         </is>
       </c>
     </row>
@@ -1173,17 +1173,17 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>화염 폭발 / 대표=화염 폭발; 투사체=성화 투사체 / 파티클=화염 폭발</t>
+          <t>화염 폭발 / 대표=화염 폭발; 투사체=파이어볼 VFX 그래프 / 파티클=화염 폭발</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>대표=화염 폭발; 투사체=성화 투사체</t>
+          <t>대표=화염 폭발; 투사체=파이어볼 VFX 그래프</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>primary=SkillVFX/Prefabs/SkillVfx_FlameBurst.prefab; projectile=SkillVFX/Prefabs/HolyFireball_Attack3.prefab</t>
+          <t>primary=SkillVFX/Prefabs/SkillVfx_FlameBurst.prefab; projectile=VFX Test/Prefab/vfx_Fireball_vfxgraph.prefab</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Assets/Data/Skills/BloodFang.asset</t>
+          <t>Assets/Data/Skills/BurnOut.asset</t>
         </is>
       </c>
     </row>
@@ -4701,17 +4701,17 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>화염 폭발 / 대표=화염 폭발; 투사체=성화 투사체; 적중 폭발=레이어드 폭발 / 파티클=화염 폭발</t>
+          <t>화염 폭발 / 대표=화염 폭발; 투사체=파이어볼 VFX 그래프; 적중 폭발=레이어드 폭발 / 파티클=화염 폭발</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>대표=화염 폭발; 투사체=성화 투사체; 적중 폭발=레이어드 폭발</t>
+          <t>대표=화염 폭발; 투사체=파이어볼 VFX 그래프; 적중 폭발=레이어드 폭발</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>primary=SkillVFX/Prefabs/SkillVfx_FlameBurst.prefab; projectile=SkillVFX/Prefabs/HolyFireball_Attack3.prefab; impact=SkillVFX/Prefabs/SkillVfx_LayeredExplosion.prefab</t>
+          <t>primary=SkillVFX/Prefabs/SkillVfx_FlameBurst.prefab; projectile=VFX Test/Prefab/vfx_Fireball_vfxgraph.prefab; impact=SkillVFX/Prefabs/SkillVfx_LayeredExplosion.prefab</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Assets/Data/Skills/OpenWound.asset</t>
+          <t>Assets/Data/Skills/BurstFireball.asset</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>HolyFireball_Attack3</t>
+          <t>vfx_Fireball_vfxgraph</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -8337,6 +8337,38 @@
       <c r="F13" t="inlineStr">
         <is>
           <t>SkillVFX/Prefabs/SkillVfx_LayeredExplosion.prefab</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>vfx_Fireball_vfxgraph</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>파이어볼 VFX 그래프</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>FireballTrail / VFX Test/Texture/FireballTrail.png; FireballTexture / VFX Test/Texture/FireballTexture.png; FireballFlare / VFX Test/Texture/FireballFlare.png</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>FireballTrail_AB / VFX Test/Materials/Fireball/FireballTrail_AB.mat; FireballTrail_Add / VFX Test/Materials/Fireball/FireballTrail_Add.mat; VisualEffect Graph / VFX Test/Prefab/vfxgraph_Fireball.vfx</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VFX Test/Prefab/vfx_Fireball_vfxgraph.prefab</t>
         </is>
       </c>
     </row>

--- a/Project 2048/Reports/Project2048_SkillVfxInventory.xlsx
+++ b/Project 2048/Reports/Project2048_SkillVfxInventory.xlsx
@@ -966,7 +966,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bleeding-cut</t>
+          <t>fireball</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>OverburnAttack</t>
+          <t>BleedAttack</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>과열 공격</t>
+          <t>화상 공격</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>적에게 위력 50 피해를 준다. 사용 후 남은 코스트를 모두 추가 소모하고, 추가 소모한 코스트 1당 위력 +10을 적용한다. 화염구를 발사한다.</t>
+          <t>화염구를 발사해 적에게 위력 50 피해를 주고, 2턴 동안 턴 종료 시 20의 화상 피해를 준다.</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1113,17 +1113,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>blood-fang</t>
+          <t>burn-out</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>불사르기</t>
+          <t>화염 소모</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>불사르기</t>
+          <t>화염 소모</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>체력 소모 공격</t>
+          <t>체력 소모 화염</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>최대 체력의 10%를 불태워 화염구를 발사하고 적에게 위력 100 피해를 준다. 이 비용으로 체력은 1 아래로 내려가지 않는다.</t>
+          <t>자신의 최대 체력 10%를 불태워 거센 화염구를 발사하고 적에게 위력 100 피해를 준다. 이 비용으로 체력은 1 아래로 내려가지 않는다.</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -4641,17 +4641,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>open-wound</t>
+          <t>burst-fireball</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>폭렬</t>
+          <t>폭발 화염구</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>폭렬</t>
+          <t>폭발 화염구</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>OverburnAttack</t>
+          <t>OpenWoundAttack</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>과열 공격</t>
+          <t>화상 연쇄 폭발</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>적에게 위력 70 피해를 준다. 사용 후 남은 코스트를 모두 추가 소모하고, 추가 소모한 코스트 1당 위력 +10을 적용한다. 폭발하는 화염구를 발사하고, 적중 시 적 위치에 폭발 이펙트를 일으킨다.</t>
+          <t>폭발하는 화염구를 발사해 적에게 위력 70 피해를 준다. 대상이 독이나 화상 상태라면 위력 +50으로 공격하고, 해당 지속 피해 시간을 1턴 연장한다.</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>적에게 위력 50 피해를 준다. 사용 후 남은 코스트를 모두 추가 소모하고, 추가 소모한 코스트 1당 위력 +10을 적용한다.</t>
+          <t>불꽃을 과열시켜 적에게 위력 50 피해를 준다. 사용 후 남은 코스트를 모두 불태우고, 추가 소모한 코스트 10당 위력 +10을 적용한다.</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>적에게 위력 110 피해를 준다. 다음 플레이어 턴의 보드 이동 횟수가 2 감소한다.</t>
+          <t>몸을 사리지 않고 불꽃을 두른 강타로 적에게 위력 110 피해를 준다. 반동으로 다음 플레이어 턴의 보드 이동 횟수가 2 감소한다.</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
